--- a/templates/000_pm_suite/01_프로젝트 관리/02_범위관리/프로젝트명_수행범위_V1.0_20230530.xlsx
+++ b/templates/000_pm_suite/01_프로젝트 관리/02_범위관리/프로젝트명_수행범위_V1.0_20230530.xlsx
@@ -518,7 +518,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[PM-10] SyncGuard AI 과업 수행범위 정의 및 확정 대비표 (Scope Statement) — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[PM-10] SyncFlow AI 과업 수행범위 정의 및 확정 대비표 (Scope Statement) — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>기술제안 및 협상 확정 범위 (SyncGuard AI)</t>
+          <t>기술제안 및 협상 확정 범위 (SyncFlow AI)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -579,12 +579,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>PDF, 이미지, 텍스트 홍보문안 자동 추출</t>
+          <t>PDF, 이미지, 텍스트 조달계약조항 자동 추출</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Upstage Document Parse + Clova OCR 하이브리드 파서 및 바운딩박스 뷰어 구축</t>
+          <t>EnterpriseVision Document Parse + Enterprise Vision OCR 하이브리드 파서 및 바운딩박스 뷰어 구축</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>표시·광고 공정화법 금지/주의 표현 필터링</t>
+          <t>하도급거래 공정화법 금지/주의 표현 필터링</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>법령·가이드라인 근거 제시 및 대체문구 생성</t>
+          <t>법령·가이드라인 근거 제시 및 표준수정조항 생성</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>사용자 심의 포털 (FO)</t>
+          <t>사용자 검증 포털 (FO)</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>마케터 심의 요청, 결과 조회, 리포트 출력</t>
+          <t>구매담당자 검증 요청, 결과 조회, 리포트 출력</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -764,12 +764,12 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>그룹 SSO, 마케팅허브, 프로덕트랩 연동</t>
+          <t>그룹 SSO, 전자구매포털, 피엘엠넥서스 연동</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>HB-SSO(OIDC), MarketingHub 양방향 API, ProductLab 전성분 02:00 일배치 연동</t>
+          <t>HB-SSO(OIDC), SRM-Portal 양방향 API, PLM-Nexus 자재BOM 02:00 일배치 연동</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
